--- a/erp-server/erp-server-file/src/main/resources/excel/tms/firstMileEstimatedBillExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/firstMileEstimatedBillExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>业务单号</t>
   </si>
@@ -76,9 +76,6 @@
     <t>预计体积重</t>
   </si>
   <si>
-    <t>结算币种</t>
-  </si>
-  <si>
     <t>运输状态</t>
   </si>
   <si>
@@ -134,9 +131,6 @@
   </si>
   <si>
     <t>{.volumeWeight}</t>
-  </si>
-  <si>
-    <t>{.currency}</t>
   </si>
   <si>
     <t>{.transportStatusName}</t>
@@ -1113,7 +1107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="13.875" customWidth="1"/>
@@ -1127,14 +1121,13 @@
     <col min="13" max="13" width="12.75" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
     <col min="15" max="15" width="11.875" customWidth="1"/>
-    <col min="16" max="16" width="9.75" customWidth="1"/>
-    <col min="17" max="17" width="14.125" customWidth="1"/>
-    <col min="18" max="18" width="15.5" customWidth="1"/>
-    <col min="19" max="19" width="14.625" customWidth="1"/>
-    <col min="20" max="20" width="15.125" customWidth="1"/>
+    <col min="16" max="16" width="14.125" customWidth="1"/>
+    <col min="17" max="17" width="15.5" customWidth="1"/>
+    <col min="18" max="18" width="14.625" customWidth="1"/>
+    <col min="19" max="19" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1" spans="1:19">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1192,70 +1185,64 @@
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:19">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:20">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>25</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>28</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>30</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>31</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>32</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>33</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>34</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>36</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>37</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/firstMileEstimatedBillExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/firstMileEstimatedBillExport.xlsx
@@ -109,19 +109,19 @@
     <t>{.feeRuleName}</t>
   </si>
   <si>
-    <t>{.costTotal}</t>
-  </si>
-  <si>
-    <t>{.logisticsCost}</t>
-  </si>
-  <si>
-    <t>{.customsClearanceCost}</t>
-  </si>
-  <si>
-    <t>{.otherTaxCost}</t>
-  </si>
-  <si>
-    <t>{.otherCost}</t>
+    <t>{.costTotalStr}</t>
+  </si>
+  <si>
+    <t>{.logisticsCostStr}</t>
+  </si>
+  <si>
+    <t>{.customsClearanceCostStr}</t>
+  </si>
+  <si>
+    <t>{.otherTaxCostStr}</t>
+  </si>
+  <si>
+    <t>{.otherCostStr}</t>
   </si>
   <si>
     <t>{.chargedWeight}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/firstMileEstimatedBillExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/firstMileEstimatedBillExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
     <t>预计物流运费（总）</t>
   </si>
   <si>
-    <t>预计报关费用（总）</t>
+    <t>预计关税费用（总）</t>
   </si>
   <si>
     <t>预计其他税费（总）</t>
